--- a/data/trans_orig/P07B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según salud mental autopercibida en 2023</t>
+          <t>Población según salud mental autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>43660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36494</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59782</t>
+          <t>60389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65905</t>
+          <t>67079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97381</t>
+          <t>96222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>251097</t>
+          <t>247205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302728</t>
+          <t>302038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>309552</t>
+          <t>308734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>433618</t>
+          <t>425226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>574701</t>
+          <t>577562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>716298</t>
+          <t>716523</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203644</t>
+          <t>205614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255463</t>
+          <t>260400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184654</t>
+          <t>185227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265115</t>
+          <t>265457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>412965</t>
+          <t>413226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510255</t>
+          <t>507325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117398</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103208</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145492</t>
+          <t>145039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208771</t>
+          <t>204670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56164</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65302</t>
+          <t>63536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91214</t>
+          <t>89839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75004</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134847</t>
+          <t>138335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>430939</t>
+          <t>428523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>867492</t>
+          <t>904724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>392445</t>
+          <t>389178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>445411</t>
+          <t>442937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>852026</t>
+          <t>851001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1386568</t>
+          <t>1371591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192165</t>
+          <t>166484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>466181</t>
+          <t>464447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287020</t>
+          <t>289940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>337872</t>
+          <t>340920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>451419</t>
+          <t>449222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>775822</t>
+          <t>778701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106865</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258315</t>
+          <t>260955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117595</t>
+          <t>119964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159772</t>
+          <t>163395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220417</t>
+          <t>218029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>389767</t>
+          <t>385221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>58077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87733</t>
+          <t>86299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67934</t>
+          <t>68179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130010</t>
+          <t>129665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>238375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>297180</t>
+          <t>296975</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>367751</t>
+          <t>364009</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>707646</t>
+          <t>713316</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>633100</t>
+          <t>631385</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1067624</t>
+          <t>1053443</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>222806</t>
+          <t>217992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>283965</t>
+          <t>280242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131665</t>
+          <t>125173</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337039</t>
+          <t>337180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>341271</t>
+          <t>334172</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>587736</t>
+          <t>587184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111269</t>
+          <t>110605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166582</t>
+          <t>167156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204457</t>
+          <t>220160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163113</t>
+          <t>168250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>332429</t>
+          <t>343728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>48993</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>82309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95460</t>
+          <t>96455</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>342616</t>
+          <t>358603</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>155149</t>
+          <t>155770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>466568</t>
+          <t>441537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410479</t>
+          <t>415004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>478936</t>
+          <t>479328</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>400920</t>
+          <t>404122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>544719</t>
+          <t>546056</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>839073</t>
+          <t>836680</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1000212</t>
+          <t>1001985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252160</t>
+          <t>251362</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>310612</t>
+          <t>308492</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>254962</t>
+          <t>237930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>341258</t>
+          <t>334355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>517944</t>
+          <t>520096</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>628300</t>
+          <t>630309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102646</t>
+          <t>105380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160993</t>
+          <t>160968</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84562</t>
+          <t>84893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132838</t>
+          <t>131698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>201549</t>
+          <t>198438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>278165</t>
+          <t>273448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>64421</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95653</t>
+          <t>97697</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>131886</t>
+          <t>134458</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>205529</t>
+          <t>205111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>267857</t>
+          <t>270319</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>581291</t>
+          <t>575203</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>435856</t>
+          <t>436001</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>808837</t>
+          <t>760096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1420385</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1994076</t>
+          <t>1985441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1602857</t>
+          <t>1611480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2143714</t>
+          <t>2122999</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3103999</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3852091</t>
+          <t>3837185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>876136</t>
+          <t>864441</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1229257</t>
+          <t>1225866</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>895490</t>
+          <t>903419</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1206696</t>
+          <t>1209433</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1916420</t>
+          <t>1944617</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2383293</t>
+          <t>2398210</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>428499</t>
+          <t>428338</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>621051</t>
+          <t>616611</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>372248</t>
+          <t>368806</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>534601</t>
+          <t>542383</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>862319</t>
+          <t>846705</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1106290</t>
+          <t>1100450</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P07B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>21851</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>47081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49040</t>
+          <t>52058</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>42098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>63285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>80577</t>
+          <t>85426</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67079</t>
+          <t>70404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96222</t>
+          <t>102530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>275445</t>
+          <t>299500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>247205</t>
+          <t>273006</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302038</t>
+          <t>324012</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>343980</t>
+          <t>320153</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>308734</t>
+          <t>297906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>425226</t>
+          <t>341132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>619426</t>
+          <t>619652</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>577562</t>
+          <t>583080</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>716523</t>
+          <t>654869</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>230539</t>
+          <t>245610</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205614</t>
+          <t>220796</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>260400</t>
+          <t>270877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>238797</t>
+          <t>256023</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185227</t>
+          <t>235371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265457</t>
+          <t>279872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>469337</t>
+          <t>501633</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>413226</t>
+          <t>466007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>507325</t>
+          <t>535522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89146</t>
+          <t>101356</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68650</t>
+          <t>81669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>83468</t>
+          <t>94971</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100616</t>
+          <t>114066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172614</t>
+          <t>196327</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145039</t>
+          <t>167615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204670</t>
+          <t>230061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18615</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>54431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,22 +1555,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75932</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63536</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89839</t>
+          <t>100155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>113482</t>
+          <t>123893</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78562</t>
+          <t>105680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138335</t>
+          <t>144382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>597580</t>
+          <t>403822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>428523</t>
+          <t>370321</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>904724</t>
+          <t>440980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>417388</t>
+          <t>469649</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>389178</t>
+          <t>442975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>442937</t>
+          <t>499561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1014969</t>
+          <t>873471</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>851001</t>
+          <t>829555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1371591</t>
+          <t>917585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>359828</t>
+          <t>401529</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166484</t>
+          <t>365128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>464447</t>
+          <t>439228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>314268</t>
+          <t>351721</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289940</t>
+          <t>322792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340920</t>
+          <t>377963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>674096</t>
+          <t>753250</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>449222</t>
+          <t>710995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>778701</t>
+          <t>799436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>191508</t>
+          <t>197321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95544</t>
+          <t>165471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260955</t>
+          <t>230750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138300</t>
+          <t>151892</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119964</t>
+          <t>130801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163395</t>
+          <t>174094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>329809</t>
+          <t>349213</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218029</t>
+          <t>309570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>387135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>43685</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>61185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62008</t>
+          <t>67001</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>53177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86299</t>
+          <t>81401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>103311</t>
+          <t>110687</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>92395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129665</t>
+          <t>133284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>267998</t>
+          <t>301276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238375</t>
+          <t>273108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>296975</t>
+          <t>333518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>502781</t>
+          <t>353057</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>364009</t>
+          <t>325991</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>713316</t>
+          <t>376942</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>770779</t>
+          <t>654333</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>631385</t>
+          <t>615585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1053443</t>
+          <t>695530</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>250657</t>
+          <t>294644</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217992</t>
+          <t>262006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>280242</t>
+          <t>325523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>251374</t>
+          <t>292399</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125173</t>
+          <t>267509</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337180</t>
+          <t>318725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>502030</t>
+          <t>587043</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>334172</t>
+          <t>547269</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>587184</t>
+          <t>625364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>136185</t>
+          <t>154428</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110605</t>
+          <t>126184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167156</t>
+          <t>187260</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>111073</t>
+          <t>93271</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59630</t>
+          <t>74731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220160</t>
+          <t>116129</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>247258</t>
+          <t>247699</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168250</t>
+          <t>214634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343728</t>
+          <t>285109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>20431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>29323</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>62597</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48993</t>
+          <t>52825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82309</t>
+          <t>87328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>163988</t>
+          <t>106223</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96455</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>358603</t>
+          <t>122432</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>226585</t>
+          <t>174143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>155770</t>
+          <t>151616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441537</t>
+          <t>199981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>480581</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>415004</t>
+          <t>447305</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>479328</t>
+          <t>512916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>498479</t>
+          <t>542065</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>404122</t>
+          <t>512467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>546056</t>
+          <t>572769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>945231</t>
+          <t>1022646</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>836680</t>
+          <t>977356</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1001985</t>
+          <t>1068536</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>279733</t>
+          <t>301867</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251362</t>
+          <t>269390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>308492</t>
+          <t>331947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>304029</t>
+          <t>328005</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>237930</t>
+          <t>301180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>334355</t>
+          <t>354243</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>583762</t>
+          <t>629873</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>520096</t>
+          <t>589814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>630309</t>
+          <t>672527</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>129461</t>
+          <t>130802</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105380</t>
+          <t>105977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160968</t>
+          <t>162845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>109626</t>
+          <t>122316</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84893</t>
+          <t>102654</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>131698</t>
+          <t>143893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>239087</t>
+          <t>253119</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198438</t>
+          <t>221579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>273448</t>
+          <t>289943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>35305</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,67 +3488,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>86672</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>71889</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>105367</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>79200</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>64421</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>97697</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>172987</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>134458</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>205111</t>
+          <t>216912</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>350968</t>
+          <t>309428</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>270319</t>
+          <t>282405</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>575203</t>
+          <t>342480</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>523955</t>
+          <t>494149</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>436001</t>
+          <t>455203</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>760096</t>
+          <t>537155</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1587776</t>
+          <t>1485178</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1422322</t>
+          <t>1422417</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1985441</t>
+          <t>1545482</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1762628</t>
+          <t>1684924</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1611480</t>
+          <t>1632239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2122999</t>
+          <t>1741361</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3350404</t>
+          <t>3170102</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3087358</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3837185</t>
+          <t>3253988</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1120757</t>
+          <t>1243650</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>864441</t>
+          <t>1176790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1225866</t>
+          <t>1300539</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1108468</t>
+          <t>1228149</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>903419</t>
+          <t>1170049</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1209433</t>
+          <t>1281728</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2229225</t>
+          <t>2471799</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1944617</t>
+          <t>2392673</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2398210</t>
+          <t>2560562</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -3905,67 +3905,67 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>546300</t>
+          <t>583907</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>428338</t>
+          <t>529966</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>616611</t>
+          <t>641010</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>462450</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>426334</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>507400</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>12,38%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>442467</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>368806</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>542383</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>988768</t>
+          <t>1046358</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>846705</t>
+          <t>978757</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1100450</t>
+          <t>1112471</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
